--- a/Statistics/Section 2 - Descriptive Statistics Fundamentals/11_Covariance/Exercises/2.11.+Covariance_exercise_solution.xlsx
+++ b/Statistics/Section 2 - Descriptive Statistics Fundamentals/11_Covariance/Exercises/2.11.+Covariance_exercise_solution.xlsx
@@ -1,26 +1,30 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="18229"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Iliya\Desktop\Statistics Course\Filming\Final excel\Section 2 - Descriptive statistics\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\slong\365 Data Science\Statistics_\Section 2 - Descriptive Statistics Fundamentals\11_Covariance_\Exercises\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE2E0734-E59A-4D8E-BD59-AB60F47769B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="10068"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Covariance" sheetId="13" r:id="rId1"/>
     <sheet name="cov" sheetId="10" state="hidden" r:id="rId2"/>
     <sheet name="Covariance2" sheetId="11" state="hidden" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="171027"/>
+  <calcPr calcId="191029"/>
   <fileRecoveryPr autoRecover="0"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -116,11 +120,11 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
-    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="165" formatCode="#,##0_);\-\ #,##0_)"/>
+    <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="166" formatCode="#,##0_);\-\ #,##0_)"/>
     <numFmt numFmtId="167" formatCode="#,##0.00_);\-\ #,##0.00_)"/>
   </numFmts>
   <fonts count="7" x14ac:knownFonts="1">
@@ -218,7 +222,7 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -227,22 +231,22 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="2" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="43" fontId="2" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="43" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="2" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="2" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="2" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="166" fontId="2" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="2" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="2" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="43" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -252,7 +256,7 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="2" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="167" fontId="2" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="167" fontId="2" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
@@ -3552,7 +3556,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="B1:M23"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="11.4" x14ac:dyDescent="0.2"/>
@@ -3566,7 +3570,8 @@
     <col min="7" max="7" width="14" style="1" customWidth="1"/>
     <col min="8" max="11" width="9.109375" style="1"/>
     <col min="12" max="12" width="4.88671875" style="1" customWidth="1"/>
-    <col min="13" max="16384" width="9.109375" style="1"/>
+    <col min="13" max="13" width="9.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:13" ht="15.6" x14ac:dyDescent="0.3">
@@ -3821,7 +3826,7 @@
       <c r="H23" s="13"/>
     </row>
   </sheetData>
-  <sortState ref="G12:G20">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="G12:G20">
     <sortCondition descending="1" ref="G12"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3831,7 +3836,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet5"/>
   <dimension ref="B1:G16"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="11.4" x14ac:dyDescent="0.2"/>
@@ -3988,7 +3993,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Sheet6"/>
   <dimension ref="B1:G16"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="11.4" x14ac:dyDescent="0.2"/>
